--- a/backend/data/attachments/trust_amendment_12.xlsx
+++ b/backend/data/attachments/trust_amendment_12.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20016</v>
+        <v>23694</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -464,7 +464,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024-02-26</t>
+          <t>2024-08-20</t>
         </is>
       </c>
     </row>
@@ -475,11 +475,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1485</v>
+        <v>698</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>7.44%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -489,7 +489,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024-02-26</t>
+          <t>2024-08-20</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>224</v>
+        <v>172</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024-02-26</t>
+          <t>2024-08-20</t>
         </is>
       </c>
     </row>
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024-02-26</t>
+          <t>2024-08-20</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>405</v>
+        <v>371</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -564,7 +564,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024-02-26</t>
+          <t>2024-08-20</t>
         </is>
       </c>
     </row>
